--- a/data/trans_camb/MCS12_SP_R2-Clase-trans_camb.xlsx
+++ b/data/trans_camb/MCS12_SP_R2-Clase-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud mental (SF12)</t>
+          <t>Población por debajo de la mediana (53.579) de la puntuación del componente de salud mental (SF12)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,67; 16,25</t>
+          <t>2,93; 16,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 13,28</t>
+          <t>0,31; 13,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 6,71</t>
+          <t>-6,29; 7,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 13,74</t>
+          <t>-3,05; 14,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,99; 5,24</t>
+          <t>-10,56; 5,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,18; 0,44</t>
+          <t>-13,04; 0,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,11; 13,42</t>
+          <t>2,83; 13,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 8,1</t>
+          <t>-2,01; 8,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 2,96</t>
+          <t>-6,2; 3,18</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,05; 43,33</t>
+          <t>7,12; 44,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 35,65</t>
+          <t>0,73; 36,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,72; 18,52</t>
+          <t>-14,2; 18,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 28,59</t>
+          <t>-5,58; 30,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-18,04; 10,99</t>
+          <t>-18,66; 11,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-23,81; 1,03</t>
+          <t>-23,8; 1,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,51; 31,6</t>
+          <t>5,61; 32,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 18,86</t>
+          <t>-4,17; 19,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-13,48; 7,06</t>
+          <t>-13,14; 7,61</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,13; 17,58</t>
+          <t>2,06; 16,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 15,19</t>
+          <t>0,07; 15,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 5,17</t>
+          <t>-10,01; 4,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,96; 17,5</t>
+          <t>1,81; 16,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 5,59</t>
+          <t>-8,84; 5,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,17; 2,12</t>
+          <t>-12,31; 1,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,33; 13,93</t>
+          <t>3,32; 13,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 7,66</t>
+          <t>-2,25; 8,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 0,67</t>
+          <t>-9,5; 0,63</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,14; 50,19</t>
+          <t>4,63; 46,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 43,05</t>
+          <t>0,17; 44,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-21,26; 14,77</t>
+          <t>-23,55; 12,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,49; 34,72</t>
+          <t>3,3; 32,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-16,11; 11,57</t>
+          <t>-14,97; 10,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,56; 3,67</t>
+          <t>-21,21; 2,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,71; 31,52</t>
+          <t>6,49; 30,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 17,57</t>
+          <t>-4,48; 18,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-19,33; 1,81</t>
+          <t>-19,04; 1,58</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,48; 14,63</t>
+          <t>2,79; 14,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 12,25</t>
+          <t>-0,17; 11,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-37,78; 1,9</t>
+          <t>-35,91; 2,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 17,98</t>
+          <t>-0,83; 18,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 14,64</t>
+          <t>-7,41; 14,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 7,39</t>
+          <t>-12,4; 6,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,02; 14,11</t>
+          <t>4,16; 14,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 10,66</t>
+          <t>-0,1; 11,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-35,4; 1,07</t>
+          <t>-32,95; 1,19</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,2; 35,34</t>
+          <t>5,89; 35,64</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 29,41</t>
+          <t>-0,45; 27,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-78,39; 4,23</t>
+          <t>-77,61; 5,35</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 35,09</t>
+          <t>-1,08; 36,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-12,7; 28,59</t>
+          <t>-11,89; 28,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-19,36; 14,57</t>
+          <t>-19,59; 12,38</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,75; 31,42</t>
+          <t>8,16; 31,64</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 23,47</t>
+          <t>-0,05; 24,65</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-71,47; 2,13</t>
+          <t>-66,82; 2,51</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 7,49</t>
+          <t>-1,39; 7,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 6,34</t>
+          <t>-1,74; 6,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,89; -1,2</t>
+          <t>-10,12; -0,88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,21; 13,05</t>
+          <t>2,13; 12,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 6,77</t>
+          <t>-3,15; 6,9</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 26,27</t>
+          <t>-6,01; 25,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,72; 8,25</t>
+          <t>2,12; 8,59</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 5,5</t>
+          <t>-0,68; 5,68</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 16,45</t>
+          <t>-5,93; 17,22</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 16,33</t>
+          <t>-2,94; 15,28</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 13,72</t>
+          <t>-3,54; 13,07</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-19,85; -2,61</t>
+          <t>-20,11; -1,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,77; 25,53</t>
+          <t>3,69; 24,54</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 13,23</t>
+          <t>-5,59; 14,04</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-12,24; 50,77</t>
+          <t>-11,1; 47,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,34; 16,95</t>
+          <t>4,07; 17,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 11,31</t>
+          <t>-1,4; 11,63</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-11,86; 33,97</t>
+          <t>-11,73; 34,87</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 10,2</t>
+          <t>-3,8; 10,77</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,12; 13,58</t>
+          <t>0,46; 13,8</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 9,73</t>
+          <t>-3,92; 10,23</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,7; 11,98</t>
+          <t>0,58; 11,93</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 9,97</t>
+          <t>-1,3; 9,93</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 9,63</t>
+          <t>-9,11; 9,59</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,37; 9,16</t>
+          <t>0,4; 9,12</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,12; 8,95</t>
+          <t>0,27; 8,99</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 8,59</t>
+          <t>-5,33; 8,63</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 26,59</t>
+          <t>-8,1; 27,39</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0,42; 36,18</t>
+          <t>0,89; 35,35</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 24,88</t>
+          <t>-8,44; 25,82</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1,08; 21,61</t>
+          <t>0,9; 21,62</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 17,99</t>
+          <t>-2,08; 17,73</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-15,61; 18,12</t>
+          <t>-15,12; 17,63</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>0,62; 18,33</t>
+          <t>0,82; 18,32</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0,17; 17,7</t>
+          <t>0,53; 18,2</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-9,44; 17,04</t>
+          <t>-9,91; 17,37</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 10,6</t>
+          <t>-4,52; 10,88</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 10,93</t>
+          <t>-4,15; 10,44</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-11,91; 10,47</t>
+          <t>-11,65; 11,75</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3,42; 11,81</t>
+          <t>3,26; 11,69</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 2,25</t>
+          <t>-5,97; 1,99</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 2,21</t>
+          <t>-6,48; 2,38</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,96; 10,18</t>
+          <t>3,11; 10,35</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 2,76</t>
+          <t>-4,93; 2,43</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 1,28</t>
+          <t>-7,45; 1,17</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-14,96; 40,4</t>
+          <t>-14,62; 41,6</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-13,68; 43,24</t>
+          <t>-12,35; 41,08</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-37,31; 40,29</t>
+          <t>-37,76; 44,48</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6,16; 23,18</t>
+          <t>5,86; 22,98</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-11,36; 4,58</t>
+          <t>-11,02; 3,98</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-12,26; 4,3</t>
+          <t>-11,88; 4,67</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5,81; 21,98</t>
+          <t>6,15; 22,22</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 5,9</t>
+          <t>-9,98; 5,24</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-15,25; 2,65</t>
+          <t>-15,06; 2,54</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>3,32; 8,33</t>
+          <t>3,29; 8,27</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2,47; 7,42</t>
+          <t>2,43; 7,34</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-13,29; -0,91</t>
+          <t>-13,79; -0,96</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5,45; 10,17</t>
+          <t>5,32; 10,09</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 3,26</t>
+          <t>-1,69; 3,29</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 9,56</t>
+          <t>-4,44; 9,05</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,84; 8,43</t>
+          <t>4,97; 8,44</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,49</t>
+          <t>1,09; 4,48</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 2,15</t>
+          <t>-7,84; 2,08</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>7,39; 19,69</t>
+          <t>7,26; 19,62</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>5,63; 17,61</t>
+          <t>5,55; 17,35</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-31,03; -2,14</t>
+          <t>-32,15; -2,28</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9,87; 19,22</t>
+          <t>9,64; 19,13</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 6,13</t>
+          <t>-3,05; 6,22</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 17,58</t>
+          <t>-8,12; 17,18</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>9,71; 17,68</t>
+          <t>10,05; 17,58</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>1,82; 9,32</t>
+          <t>2,18; 9,24</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-15,14; 4,3</t>
+          <t>-16,04; 4,26</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/MCS12_SP_R2-Clase-trans_camb.xlsx
+++ b/data/trans_camb/MCS12_SP_R2-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>0,83</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-6,22</t>
+          <t>-5,41</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,66</t>
+          <t>-1,34</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,93; 16,52</t>
+          <t>3,33; 16,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 13,33</t>
+          <t>-0,16; 14,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 7,03</t>
+          <t>-5,42; 7,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 14,16</t>
+          <t>-2,44; 13,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,56; 5,55</t>
+          <t>-10,48; 5,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,04; 0,69</t>
+          <t>-12,07; 2,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,83; 13,6</t>
+          <t>3,12; 14,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 8,27</t>
+          <t>-2,35; 8,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 3,18</t>
+          <t>-5,74; 3,61</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-12,26%</t>
+          <t>-10,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-3,7%</t>
+          <t>-2,99%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,12; 44,71</t>
+          <t>7,51; 43,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 36,42</t>
+          <t>-0,34; 36,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-14,2; 18,77</t>
+          <t>-11,95; 20,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 30,02</t>
+          <t>-4,5; 29,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-18,66; 11,96</t>
+          <t>-18,85; 12,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-23,8; 1,56</t>
+          <t>-22,13; 4,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,61; 32,05</t>
+          <t>6,4; 33,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 19,72</t>
+          <t>-4,94; 19,46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-13,14; 7,61</t>
+          <t>-12,23; 8,62</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-2,35</t>
+          <t>-2,46</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-5,52</t>
+          <t>-5,43</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-4,52</t>
+          <t>-4,42</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,06; 16,3</t>
+          <t>2,16; 16,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 15,25</t>
+          <t>-0,02; 14,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,01; 4,35</t>
+          <t>-9,21; 4,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 16,45</t>
+          <t>1,7; 17,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 5,42</t>
+          <t>-9,25; 5,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 1,17</t>
+          <t>-12,37; 1,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,32; 13,75</t>
+          <t>2,76; 13,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 8,09</t>
+          <t>-2,28; 7,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 0,63</t>
+          <t>-8,49; 0,68</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-6,04%</t>
+          <t>-6,31%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-10,06%</t>
+          <t>-9,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-9,63%</t>
+          <t>-9,42%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,63; 46,02</t>
+          <t>4,95; 47,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 44,16</t>
+          <t>0,08; 39,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-23,55; 12,04</t>
+          <t>-21,71; 11,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,3; 32,84</t>
+          <t>3,68; 33,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-14,97; 10,73</t>
+          <t>-15,75; 11,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-21,21; 2,14</t>
+          <t>-20,83; 2,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,49; 30,67</t>
+          <t>5,25; 30,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 18,26</t>
+          <t>-4,62; 18,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-19,04; 1,58</t>
+          <t>-17,28; 1,34</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-16,39</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-3,3</t>
+          <t>-3,19</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-14,24</t>
+          <t>-0,3</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,79; 14,59</t>
+          <t>2,25; 14,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 11,93</t>
+          <t>-0,32; 11,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-35,91; 2,56</t>
+          <t>-6,76; 6,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 18,04</t>
+          <t>-1,42; 18,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 14,47</t>
+          <t>-7,14; 14,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 6,46</t>
+          <t>-12,22; 7,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,16; 14,28</t>
+          <t>4,09; 14,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 11,06</t>
+          <t>-0,61; 10,82</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-32,95; 1,19</t>
+          <t>-5,76; 5,01</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-36,57%</t>
+          <t>0,01%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-5,75%</t>
+          <t>-5,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-29,79%</t>
+          <t>-0,62%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,89; 35,64</t>
+          <t>4,59; 35,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 27,89</t>
+          <t>-0,47; 27,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-77,61; 5,35</t>
+          <t>-14,1; 14,05</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 36,58</t>
+          <t>-2,04; 35,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 28,31</t>
+          <t>-11,24; 27,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-19,59; 12,38</t>
+          <t>-19,54; 14,68</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,16; 31,64</t>
+          <t>7,82; 31,93</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 24,65</t>
+          <t>-1,07; 23,74</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-66,82; 2,51</t>
+          <t>-11,42; 11,17</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-5,33</t>
+          <t>-4,94</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,87</t>
+          <t>-4,0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,75</t>
+          <t>-4,19</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 7,09</t>
+          <t>-0,9; 7,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 6,05</t>
+          <t>-1,93; 5,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,12; -0,88</t>
+          <t>-9,33; -0,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,13; 12,46</t>
+          <t>2,08; 12,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 6,9</t>
+          <t>-2,79; 7,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 25,59</t>
+          <t>-8,55; 0,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,12; 8,59</t>
+          <t>1,66; 8,35</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 5,68</t>
+          <t>-0,84; 5,39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 17,22</t>
+          <t>-7,36; -0,95</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-11,04%</t>
+          <t>-10,24%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>-7,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>-8,35%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 15,28</t>
+          <t>-1,8; 16,47</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 13,07</t>
+          <t>-3,89; 12,22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-20,11; -1,9</t>
+          <t>-18,6; -1,7</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,69; 24,54</t>
+          <t>3,91; 25,06</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 14,04</t>
+          <t>-4,92; 14,23</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-11,1; 47,9</t>
+          <t>-15,42; 1,29</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,07; 17,56</t>
+          <t>3,33; 17,28</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 11,63</t>
+          <t>-1,65; 11,13</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-11,73; 34,87</t>
+          <t>-14,12; -1,94</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3,23</t>
+          <t>2,29</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-1,87</t>
+          <t>-3,52</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>-1,53</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 10,77</t>
+          <t>-3,15; 9,61</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,46; 13,8</t>
+          <t>0,37; 13,93</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 10,23</t>
+          <t>-4,35; 9,99</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,58; 11,93</t>
+          <t>0,35; 11,68</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 9,93</t>
+          <t>-1,18; 10,09</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 9,59</t>
+          <t>-8,69; 1,52</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,4; 9,12</t>
+          <t>0,37; 9,04</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,27; 8,99</t>
+          <t>0,3; 8,94</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 8,63</t>
+          <t>-5,99; 2,15</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-3,2%</t>
+          <t>-6,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>-2,92%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 27,39</t>
+          <t>-6,85; 24,68</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0,89; 35,35</t>
+          <t>0,76; 35,93</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 25,82</t>
+          <t>-9,42; 25,5</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>0,9; 21,62</t>
+          <t>0,65; 21,28</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 17,73</t>
+          <t>-1,98; 18,15</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-15,12; 17,63</t>
+          <t>-14,06; 2,69</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>0,82; 18,32</t>
+          <t>0,6; 18,03</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0,53; 18,2</t>
+          <t>0,5; 17,66</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 17,37</t>
+          <t>-10,75; 4,33</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-2,29</t>
+          <t>-0,18</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-1,83</t>
+          <t>-2,3</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-3,11</t>
+          <t>-2,51</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 10,88</t>
+          <t>-4,71; 11,03</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 10,44</t>
+          <t>-4,63; 10,38</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 11,75</t>
+          <t>-10,21; 9,81</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3,26; 11,69</t>
+          <t>3,06; 11,4</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 1,99</t>
+          <t>-5,92; 2,22</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 2,38</t>
+          <t>-6,56; 2,29</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,11; 10,35</t>
+          <t>2,89; 10,11</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 2,43</t>
+          <t>-5,09; 2,48</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 1,17</t>
+          <t>-6,61; 1,56</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-7,87%</t>
+          <t>-0,61%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-3,46%</t>
+          <t>-4,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-6,46%</t>
+          <t>-5,2%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-14,62; 41,6</t>
+          <t>-15,05; 43,56</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-12,35; 41,08</t>
+          <t>-15,11; 40,2</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-37,76; 44,48</t>
+          <t>-31,97; 38,59</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5,86; 22,98</t>
+          <t>5,75; 22,54</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-11,02; 3,98</t>
+          <t>-10,76; 4,43</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-11,88; 4,67</t>
+          <t>-12,18; 4,4</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6,15; 22,22</t>
+          <t>5,83; 21,98</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-9,98; 5,24</t>
+          <t>-10,41; 5,3</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-15,06; 2,54</t>
+          <t>-13,32; 3,39</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-4,91</t>
+          <t>-1,63</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-0,42</t>
+          <t>-3,52</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-2,53</t>
+          <t>-2,54</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>3,29; 8,27</t>
+          <t>3,16; 8,06</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2,43; 7,34</t>
+          <t>2,38; 7,2</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-13,79; -0,96</t>
+          <t>-4,17; 1,19</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5,32; 10,09</t>
+          <t>5,18; 9,91</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 3,29</t>
+          <t>-1,71; 2,98</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 9,05</t>
+          <t>-5,83; -1,17</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,97; 8,44</t>
+          <t>4,9; 8,39</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,09; 4,48</t>
+          <t>1,19; 4,61</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 2,08</t>
+          <t>-4,29; -0,94</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-11,36%</t>
+          <t>-3,77%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-0,77%</t>
+          <t>-6,51%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-5,19%</t>
+          <t>-5,21%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>7,26; 19,62</t>
+          <t>7,1; 19,39</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>5,55; 17,35</t>
+          <t>5,35; 17,18</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-32,15; -2,28</t>
+          <t>-9,35; 2,84</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9,64; 19,13</t>
+          <t>9,31; 18,7</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 6,22</t>
+          <t>-3,1; 5,68</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 17,18</t>
+          <t>-10,51; -2,23</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>10,05; 17,58</t>
+          <t>9,83; 17,45</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2,18; 9,24</t>
+          <t>2,39; 9,57</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-16,04; 4,26</t>
+          <t>-8,68; -2,02</t>
         </is>
       </c>
     </row>
